--- a/template/template.xlsx
+++ b/template/template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowHeight="16660" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1001,6 +1001,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1095,17 +1106,6 @@
         <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1424,7 +1424,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1464,18 +1464,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1530,17 +1542,26 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1557,6 +1578,9 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1572,6 +1596,9 @@
     <xf numFmtId="0" fontId="13" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1587,38 +1614,38 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1626,13 +1653,16 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1665,10 +1695,10 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1746,15 +1776,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>105410</xdr:colOff>
+      <xdr:colOff>52705</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>95885</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2123440</xdr:colOff>
+      <xdr:colOff>2070735</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>979170</xdr:rowOff>
+      <xdr:rowOff>989330</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1771,7 +1801,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="867410" y="5271135"/>
+          <a:off x="814705" y="5233670"/>
           <a:ext cx="4202430" cy="1340485"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2046,368 +2076,413 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="3" width="28.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="12.1666666666667" customWidth="1"/>
-    <col min="5" max="5" width="9.33333333333333" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="5.66666666666667" customWidth="1"/>
-    <col min="8" max="8" width="12.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="4" max="6" width="12.1666666666667" customWidth="1"/>
+    <col min="7" max="7" width="9.33333333333333" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="5.66666666666667" customWidth="1"/>
+    <col min="10" max="10" width="12.6666666666667" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.95" spans="1:9">
-      <c r="B1" s="18" t="s">
+    <row r="1" ht="23.95" spans="1:11">
+      <c r="B1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-    </row>
-    <row r="2" ht="18.35" spans="1:9">
-      <c r="B2" s="19" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="B2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21" t="s">
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="20" t="s">
+      <c r="G2" s="25"/>
+      <c r="H2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="I2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="23"/>
-      <c r="I2" s="24"/>
-    </row>
-    <row r="3" ht="18.35" spans="1:9">
-      <c r="B3" s="25" t="s">
+      <c r="J2" s="27"/>
+      <c r="K2" s="28"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="B3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="27" t="s">
+      <c r="C3" s="30"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="29"/>
-    </row>
-    <row r="4" ht="18.35" spans="1:9">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="33"/>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="33"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="37"/>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="G5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="H5" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="I5" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="J5" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="K5" s="43" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1" spans="1:9">
+    <row r="6" ht="33" customHeight="1" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="42">
+      <c r="B6" s="44"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="49">
         <f>B6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="1:9">
+    <row r="7" ht="33" customHeight="1" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="47">
-        <f>G7</f>
+      <c r="B7" s="50"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55">
+        <f>I7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" spans="1:9">
+    <row r="8" ht="33" customHeight="1" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="52">
-        <f>H8</f>
+      <c r="B8" s="56"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61">
+        <f>J8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="G9" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="H9" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="53" t="s">
+      <c r="I9" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="J9" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="53" t="s">
+      <c r="K9" s="62" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="80" t="s">
+      <c r="B10" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="C10" s="65"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="D11" s="81" t="s">
+      <c r="B11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="53"/>
-      <c r="F11" s="55"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="G11" s="62"/>
+      <c r="H11" s="65"/>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="B13" s="58" t="s">
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="61" t="s">
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="63"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="B14" s="64"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="67" t="s">
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="74"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="68">
-        <f>COUNTA(H6:H8)</f>
+      <c r="I14" s="78">
+        <f>COUNTA(J6:J8)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="69"/>
-      <c r="I14" s="70"/>
-    </row>
-    <row r="15" ht="18.35" spans="1:9">
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="74" t="s">
+      <c r="J14" s="79"/>
+      <c r="K14" s="80"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="81"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="75">
-        <f>SUM(I6:I8)</f>
+      <c r="I15" s="85">
+        <f>SUM(K6:K8)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="76"/>
-      <c r="I15" s="77"/>
-    </row>
-    <row r="16" ht="18.35" spans="1:9">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53" t="s">
+      <c r="J15" s="86"/>
+      <c r="K15" s="87"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="62"/>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="78" t="s">
+    <row r="18" spans="2:11">
+      <c r="B18" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="78"/>
-      <c r="D18" s="53" t="s">
+      <c r="C18" s="88"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="53"/>
-      <c r="F18" s="78" t="s">
+      <c r="G18" s="62"/>
+      <c r="H18" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="78"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="78" t="s">
+      <c r="I18" s="88"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="78"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="78" t="s">
+      <c r="C19" s="88"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="78" t="s">
+      <c r="I19" s="88"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="78"/>
-      <c r="D20" s="79" t="s">
+      <c r="C20" s="88"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="53"/>
-      <c r="F20" s="78" t="s">
+      <c r="G20" s="62"/>
+      <c r="H20" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="16" t="s">
+      <c r="I20" s="88"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="88"/>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="16"/>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-    </row>
-    <row r="23" ht="84" customHeight="1" spans="2:9">
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
+      <c r="C21" s="19"/>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+    </row>
+    <row r="23" ht="84" customHeight="1" spans="2:11">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="B1:I1"/>
+  <mergeCells count="25">
+    <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="I2:K2"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="F3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="H19:I19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
     <mergeCell ref="B21:C23"/>
-    <mergeCell ref="B14:E15"/>
+    <mergeCell ref="B14:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2418,7 +2493,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2426,10 +2501,10 @@
     <col min="3" max="4" width="9.33333333333333" customWidth="1"/>
     <col min="5" max="5" width="32.3333333333333" customWidth="1"/>
     <col min="6" max="6" width="9.33333333333333" customWidth="1"/>
-    <col min="8" max="9" width="9.33333333333333" customWidth="1"/>
+    <col min="8" max="10" width="9.33333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1"/>
       <c r="B1" s="10"/>
       <c r="C1" s="11" t="s">
@@ -2441,8 +2516,9 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1"/>
       <c r="B2" s="10" t="s">
         <v>42</v>
@@ -2458,8 +2534,9 @@
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1"/>
       <c r="B3" s="10" t="s">
         <v>45</v>
@@ -2471,8 +2548,9 @@
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
-    </row>
-    <row r="4" ht="31.6" spans="1:9">
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" ht="31.6" spans="1:10">
       <c r="A4" s="12" t="s">
         <v>7</v>
       </c>
@@ -2486,8 +2564,9 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2512,43 +2591,46 @@
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="13" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="15">
         <f>F6+H6</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="14">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="15">
         <f>F7+H7</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="16"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -2573,32 +2655,37 @@
       <c r="H8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="82" t="s">
+      <c r="D9" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="16"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="E9" s="19"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="82" t="s">
+      <c r="B10" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="17" t="s">
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="21" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
@@ -2607,11 +2694,11 @@
       <c r="G11" t="s">
         <v>53</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="20" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12" s="1"/>
       <c r="B12" s="11" t="s">
         <v>41</v>
@@ -2623,8 +2710,9 @@
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1"/>
       <c r="B13" s="11" t="s">
         <v>55</v>
@@ -2636,8 +2724,9 @@
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="1"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2647,17 +2736,18 @@
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="G15" s="9" t="s">
         <v>56</v>
       </c>
       <c r="H15">
-        <f>SUM(I6:I7)</f>
+        <f>SUM(J6:J7)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:10">
       <c r="G16" s="9" t="s">
         <v>57</v>
       </c>
@@ -2667,11 +2757,18 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="13">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="D9:E9"/>
+    <mergeCell ref="I9:J9"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:H14"/>
   </mergeCells>

--- a/template/template.xlsx
+++ b/template/template.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="57">
   <si>
     <t>测试客户商城对账单</t>
   </si>
@@ -206,9 +206,6 @@
   </si>
   <si>
     <t>分类</t>
-  </si>
-  <si>
-    <t>计数</t>
   </si>
   <si>
     <t>求和</t>
@@ -2691,11 +2688,8 @@
       <c r="C11" t="s">
         <v>52</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" s="20" t="s">
         <v>53</v>
-      </c>
-      <c r="I11" s="20" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2715,7 +2709,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="1"/>
       <c r="B13" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -2740,7 +2734,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="G15" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H15">
         <f>SUM(J6:J7)</f>
@@ -2749,7 +2743,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="G16" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H16">
         <f>COUNTA(H6:H7)</f>
@@ -2896,12 +2890,12 @@
         <v>52</v>
       </c>
       <c r="I6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <f>SUM(H3:H4)</f>
@@ -2910,7 +2904,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <f>COUNTA(B3:B4)</f>

--- a/template/template.xlsx
+++ b/template/template.xlsx
@@ -4,13 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660" activeTab="1"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">Sheet2!$1:$5</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1421,7 +1425,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1482,9 +1486,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1545,9 +1546,6 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1615,9 +1613,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
@@ -1798,7 +1793,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="814705" y="5233670"/>
+          <a:off x="814705" y="5281295"/>
           <a:ext cx="4202430" cy="1340485"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2072,7 +2067,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
   <cols>
@@ -2083,104 +2080,104 @@
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="5.66666666666667" customWidth="1"/>
     <col min="10" max="10" width="12.6666666666667" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="11" max="11" width="24.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.95" spans="1:11">
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="B2" s="23" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+    </row>
+    <row r="2" ht="18.35" spans="1:11">
+      <c r="B2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="24" t="s">
+      <c r="G2" s="24"/>
+      <c r="H2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="27"/>
-      <c r="K2" s="28"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="B3" s="29" t="s">
+      <c r="J2" s="26"/>
+      <c r="K2" s="27"/>
+    </row>
+    <row r="3" ht="18.35" spans="1:11">
+      <c r="B3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="33"/>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+    </row>
+    <row r="4" ht="18.35" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="37"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="36"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="41" t="s">
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="41" t="s">
+      <c r="J5" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="41" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2188,16 +2185,16 @@
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="49">
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="47">
         <f>B6</f>
         <v>0</v>
       </c>
@@ -2206,16 +2203,16 @@
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
-      <c r="K7" s="55">
+      <c r="B7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="53">
         <f>I7</f>
         <v>0</v>
       </c>
@@ -2224,16 +2221,16 @@
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="61">
+      <c r="B8" s="54"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="59">
         <f>J8</f>
         <v>0</v>
       </c>
@@ -2242,30 +2239,30 @@
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="62" t="s">
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="62" t="s">
+      <c r="G9" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="62" t="s">
+      <c r="H9" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="62" t="s">
+      <c r="I9" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="62" t="s">
+      <c r="J9" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="62" t="s">
+      <c r="K9" s="60" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2273,171 +2270,171 @@
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="91" t="s">
+      <c r="B11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="62"/>
-      <c r="H11" s="65"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="61"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="71" t="s">
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="73"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="70"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="B14" s="74"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="77" t="s">
+      <c r="B14" s="71"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="78">
+      <c r="I14" s="75">
         <f>COUNTA(J6:J8)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="79"/>
-      <c r="K14" s="80"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="B15" s="81"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="84" t="s">
+      <c r="J14" s="76"/>
+      <c r="K14" s="77"/>
+    </row>
+    <row r="15" ht="18.35" spans="1:11">
+      <c r="B15" s="78"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="85">
+      <c r="I15" s="82">
         <f>SUM(K6:K8)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="86"/>
-      <c r="K15" s="87"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="62"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="84"/>
+    </row>
+    <row r="16" ht="18.35" spans="1:11">
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
     </row>
     <row r="17" spans="2:11">
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62" t="s">
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="2:11">
-      <c r="B18" s="88" t="s">
+      <c r="B18" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="88"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62" t="s">
+      <c r="C18" s="85"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="62"/>
-      <c r="H18" s="88" t="s">
+      <c r="G18" s="60"/>
+      <c r="H18" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="88"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="88" t="s">
+      <c r="B19" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="88"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="88" t="s">
+      <c r="C19" s="85"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="88"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="85"/>
+      <c r="K19" s="85"/>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="88" t="s">
+      <c r="B20" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="88"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89" t="s">
+      <c r="C20" s="85"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="G20" s="62"/>
-      <c r="H20" s="88" t="s">
+      <c r="G20" s="60"/>
+      <c r="H20" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="I20" s="88"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
+      <c r="K20" s="85"/>
     </row>
     <row r="21" spans="2:11">
       <c r="B21" s="19" t="s">
@@ -2481,7 +2478,7 @@
     <mergeCell ref="B21:C23"/>
     <mergeCell ref="B14:G15"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.251388888888889" right="0.251388888888889" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2489,7 +2486,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
   <cols>
@@ -2661,34 +2660,34 @@
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="92" t="s">
+      <c r="D9" s="89" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="19"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="89" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="19" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2766,14 +2765,16 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:H14"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.251388888888889" right="0.251388888888889" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
   <sheetData>
@@ -2915,7 +2916,7 @@
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.298611111111111" footer="0.298611111111111"/>
   <headerFooter/>
 </worksheet>
 </file>